--- a/data/trans_orig/IP18A03-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP18A03-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47847</t>
+          <t>47489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63134</t>
+          <t>62570</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46791</t>
+          <t>46331</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60972</t>
+          <t>60789</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98694</t>
+          <t>98519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120022</t>
+          <t>120042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>31935</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46658</t>
+          <t>47016</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25142</t>
+          <t>25325</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39323</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60597</t>
+          <t>60577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81925</t>
+          <t>82100</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41091</t>
+          <t>40839</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54922</t>
+          <t>54846</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38923</t>
+          <t>38133</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>51760</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82388</t>
+          <t>84197</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102522</t>
+          <t>102958</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,15%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25363</t>
+          <t>25439</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39194</t>
+          <t>39446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23367</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36445</t>
+          <t>37235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53131</t>
+          <t>52695</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73265</t>
+          <t>71456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36778</t>
+          <t>36845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48162</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54756</t>
+          <t>54368</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67705</t>
+          <t>67679</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94799</t>
+          <t>95143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113262</t>
+          <t>112798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11927</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23311</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17784</t>
+          <t>17810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30733</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32316</t>
+          <t>32780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50779</t>
+          <t>50435</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95498</t>
+          <t>96061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115558</t>
+          <t>115826</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103690</t>
+          <t>102639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122943</t>
+          <t>122183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>205178</t>
+          <t>203570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>232683</t>
+          <t>232483</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56875</t>
+          <t>56607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76935</t>
+          <t>76372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53539</t>
+          <t>54299</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72792</t>
+          <t>73843</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116231</t>
+          <t>116431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>143736</t>
+          <t>145344</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,66%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44167</t>
+          <t>43126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58725</t>
+          <t>57816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59120</t>
+          <t>59875</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74148</t>
+          <t>75031</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107823</t>
+          <t>107017</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129346</t>
+          <t>128154</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>67,97%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27113</t>
+          <t>28022</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41671</t>
+          <t>42712</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28552</t>
+          <t>27669</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43580</t>
+          <t>42825</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59192</t>
+          <t>60384</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80715</t>
+          <t>81521</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,24%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43796</t>
+          <t>43842</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55690</t>
+          <t>55238</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37888</t>
+          <t>36459</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49667</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84371</t>
+          <t>84617</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101435</t>
+          <t>101862</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>24928</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16710</t>
+          <t>16758</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28489</t>
+          <t>29918</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33712</t>
+          <t>33285</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50776</t>
+          <t>50530</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>334281</t>
+          <t>334325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>370526</t>
+          <t>371849</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>364758</t>
+          <t>365922</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>401910</t>
+          <t>403847</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>710863</t>
+          <t>710826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>763470</t>
+          <t>765220</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>191394</t>
+          <t>190071</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>227639</t>
+          <t>227595</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>190618</t>
+          <t>188681</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>227770</t>
+          <t>226606</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>390978</t>
+          <t>389228</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>443585</t>
+          <t>443622</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50524</t>
+          <t>50185</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64425</t>
+          <t>64370</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50343</t>
+          <t>50383</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64824</t>
+          <t>64688</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106903</t>
+          <t>104714</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>126688</t>
+          <t>125059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>73,67%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>19523</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33369</t>
+          <t>33708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21037</t>
+          <t>21173</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35518</t>
+          <t>35478</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43065</t>
+          <t>44694</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62850</t>
+          <t>65039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50565</t>
+          <t>51001</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66099</t>
+          <t>65461</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44011</t>
+          <t>43910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58673</t>
+          <t>58829</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100178</t>
+          <t>100259</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121340</t>
+          <t>121369</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,33%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23321</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29519</t>
+          <t>29363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44181</t>
+          <t>44282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56271</t>
+          <t>56242</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77433</t>
+          <t>77352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,55%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50534</t>
+          <t>50303</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63886</t>
+          <t>64399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54334</t>
+          <t>54226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67388</t>
+          <t>67633</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108862</t>
+          <t>110249</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127380</t>
+          <t>128698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,19%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17745</t>
+          <t>17232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31097</t>
+          <t>31328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15575</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28629</t>
+          <t>28737</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37214</t>
+          <t>35896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55732</t>
+          <t>54345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101864</t>
+          <t>102770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124061</t>
+          <t>125212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124829</t>
+          <t>125607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147293</t>
+          <t>147793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>234826</t>
+          <t>236033</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>265997</t>
+          <t>267528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,37%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68524</t>
+          <t>67373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90721</t>
+          <t>89815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69390</t>
+          <t>68890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91854</t>
+          <t>91076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143272</t>
+          <t>141741</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>174443</t>
+          <t>173236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85861</t>
+          <t>84851</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103776</t>
+          <t>102715</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80798</t>
+          <t>80911</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99537</t>
+          <t>99542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>173185</t>
+          <t>172294</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>197191</t>
+          <t>197639</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33189</t>
+          <t>34250</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51104</t>
+          <t>52114</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34931</t>
+          <t>34926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53670</t>
+          <t>53557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74242</t>
+          <t>73794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98248</t>
+          <t>99139</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>25529</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>37652</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>36190</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49687</t>
+          <t>50387</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66861</t>
+          <t>67678</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84577</t>
+          <t>84854</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,13%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>27131</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20406</t>
+          <t>19706</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33509</t>
+          <t>33903</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>37899</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55892</t>
+          <t>55075</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>44,87%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>395498</t>
+          <t>395522</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>434322</t>
+          <t>434952</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>420782</t>
+          <t>422581</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>462809</t>
+          <t>461586</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>827226</t>
+          <t>828572</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>885900</t>
+          <t>883455</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,16%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>202832</t>
+          <t>202202</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241656</t>
+          <t>241632</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>215450</t>
+          <t>216673</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>257477</t>
+          <t>255678</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>429513</t>
+          <t>431958</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>488187</t>
+          <t>486841</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39469</t>
+          <t>39486</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53358</t>
+          <t>53074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52324</t>
+          <t>52023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66977</t>
+          <t>66854</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95205</t>
+          <t>95431</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115844</t>
+          <t>115606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23385</t>
+          <t>23669</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37274</t>
+          <t>37257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25974</t>
+          <t>26097</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40627</t>
+          <t>40928</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53850</t>
+          <t>54088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74489</t>
+          <t>74263</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,76%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51903</t>
+          <t>51934</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67031</t>
+          <t>66985</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50916</t>
+          <t>49548</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67316</t>
+          <t>66334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107886</t>
+          <t>107321</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129259</t>
+          <t>129728</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,76%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29400</t>
+          <t>29446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44528</t>
+          <t>44497</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30563</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46963</t>
+          <t>48331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65050</t>
+          <t>64581</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86423</t>
+          <t>86988</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29146</t>
+          <t>29651</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40383</t>
+          <t>40691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33068</t>
+          <t>33765</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46321</t>
+          <t>46754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67637</t>
+          <t>67351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84832</t>
+          <t>84145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24447</t>
+          <t>23942</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21183</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34436</t>
+          <t>33739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36264</t>
+          <t>36951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53459</t>
+          <t>53745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>127478</t>
+          <t>126904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149274</t>
+          <t>148697</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115675</t>
+          <t>115127</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136079</t>
+          <t>136128</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>248443</t>
+          <t>249295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>278856</t>
+          <t>279764</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,58%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58110</t>
+          <t>58687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79906</t>
+          <t>80480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52936</t>
+          <t>52887</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73340</t>
+          <t>73888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117542</t>
+          <t>116634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147955</t>
+          <t>147103</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78959</t>
+          <t>78529</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>95245</t>
+          <t>94953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84101</t>
+          <t>84021</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100728</t>
+          <t>100688</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>166755</t>
+          <t>167790</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190667</t>
+          <t>191515</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30363</t>
+          <t>30655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46649</t>
+          <t>47079</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28706</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45333</t>
+          <t>45413</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64375</t>
+          <t>63527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88287</t>
+          <t>87252</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24086</t>
+          <t>24385</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36788</t>
+          <t>37049</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31114</t>
+          <t>31422</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>43665</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59031</t>
+          <t>58952</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77046</t>
+          <t>76034</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>64,58%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32222</t>
+          <t>31923</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17572</t>
+          <t>17762</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30313</t>
+          <t>30005</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40689</t>
+          <t>41701</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58704</t>
+          <t>58783</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>378225</t>
+          <t>378016</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>417870</t>
+          <t>416858</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>395025</t>
+          <t>394233</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>437615</t>
+          <t>434283</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>784716</t>
+          <t>785693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>840387</t>
+          <t>843437</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,24%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>198196</t>
+          <t>199208</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>237841</t>
+          <t>238050</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>200594</t>
+          <t>203926</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>243184</t>
+          <t>243976</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>413888</t>
+          <t>410838</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>469559</t>
+          <t>468582</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16307</t>
+          <t>15654</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22862</t>
+          <t>22684</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11465</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18584</t>
+          <t>18460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30115</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39830</t>
+          <t>40031</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15196</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9883</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>11054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>15598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18303</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24848</t>
+          <t>24849</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>59,94%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17513</t>
+          <t>17914</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25721</t>
+          <t>25882</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27756</t>
+          <t>28240</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36698</t>
+          <t>36549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49516</t>
+          <t>48788</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60873</t>
+          <t>60851</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>12288</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12890</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21816</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>18946</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21919</t>
+          <t>21493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27789</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37132</t>
+          <t>36683</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45516</t>
+          <t>45264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13211</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8953</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19493</t>
+          <t>19277</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>408</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>570</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69582</t>
+          <t>69641</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83206</t>
+          <t>83413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>94941</t>
+          <t>95748</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>110961</t>
+          <t>111241</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>170886</t>
+          <t>169795</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>190848</t>
+          <t>190333</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15473</t>
+          <t>15266</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29097</t>
+          <t>29038</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19401</t>
+          <t>19121</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35421</t>
+          <t>34614</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58156</t>
+          <t>59247</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
